--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>9956.65</v>
+        <v>9948.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.7348484848484849</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>312.4144963915908</v>
+        <v>312.3437990580848</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.2258298207976208</v>
+        <v>0.2255787753875711</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03137747097583934</v>
+        <v>0.03139717425431711</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>25.75757575757576</v>
+        <v>26.51515151515152</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>95.16596415952417</v>
+        <v>95.11575507751422</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>46.58009227816028</v>
+        <v>47.09533258386033</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>27.41441780666432</v>
+        <v>27.40854334406916</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8564.661532937695</v>
+        <v>8560.888554734745</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.1398049009518568</v>
+        <v>-0.139449188569257</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>32.6579500955521</v>
+        <v>32.64927826981638</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10202.81703228362</v>
+        <v>10197.79961129902</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.02472388125359593</v>
+        <v>0.02509507911511388</v>
       </c>
     </row>
     <row r="15"/>
@@ -4103,7 +4103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4194,6 +4194,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>9948.15</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.734848484848</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.225578775388</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>9948.15</v>
+        <v>9904.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>31.85</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.7348484848484849</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>312.3437990580848</v>
+        <v>312.3573005361085</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.2255787753875711</v>
+        <v>0.2253901090176604</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03139717425431711</v>
+        <v>0.0315357931251971</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>26.51515151515152</v>
+        <v>29.54545454545454</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>95.11575507751422</v>
+        <v>95.0780218035321</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>47.09533258386033</v>
+        <v>49.2052247228778</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>27.40854334406916</v>
+        <v>27.40412855101326</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8560.888554734745</v>
+        <v>8559.879617739</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.139449188569257</v>
+        <v>-0.1357890712389386</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>32.64927826981638</v>
+        <v>32.6427611943529</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10197.79961129902</v>
+        <v>10196.20476871291</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.02509507911511388</v>
+        <v>0.02941536406032474</v>
       </c>
     </row>
     <row r="15"/>
@@ -4103,7 +4103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4227,6 +4227,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>9904.85</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.7045454545449999</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.225390109018</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>9904.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>31.71</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.7045454545454546</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>312.3573005361085</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.2253901090176604</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>29.54545454545454</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>95.0780218035321</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>49.2052247228778</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>27.40412855101326</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>8559.879617739</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>-0.1357890712389386</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>32.6427611943529</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>10196.20476871291</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.02941536406032474</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.7155843521975742</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.2531707247144392</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.33357679173794</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.1777069814551362</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1615917918332266</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.2600859628423946</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,19 +857,19 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.1622127236202262</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1990509240348866</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1453087958047855</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.1166920027361642</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -867,17 +882,17 @@
       <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.1126363834223368</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>-0.0105997250482171</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.0466425678305542</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -890,21 +905,20 @@
       <c r="B22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>-0.08813546435534414</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.005035411055723138</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1070272331117028</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1040,16 +1054,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>4283.05</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>82.79000000000001</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1059,16 +1073,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>4620.65</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>70.56</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1078,16 +1092,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>4891.35</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>60.54</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1097,16 +1111,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>5292.5</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>34.69</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1116,16 +1130,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>5135.35</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>37.73</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1135,16 +1149,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>5340.7</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>29.25</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1154,16 +1168,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>5250.7</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>33.17</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1173,16 +1187,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>5078.65</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>31.57</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1192,16 +1206,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>5330.75</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>33.52</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1211,16 +1225,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>5161.8</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>33.05</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1230,16 +1244,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>4514.6</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>28.87</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1249,16 +1263,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>4801.45</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>31.59</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1268,16 +1282,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>4719.2</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>30.39</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1287,16 +1301,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>4194.15</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>24.37</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1306,16 +1320,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>3848.55</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>22.84</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1325,16 +1339,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>4205.9</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>22.85</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1344,16 +1358,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>4399</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>22.75</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1363,16 +1377,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>4265.9</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>19.04</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1382,16 +1396,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>4310.4</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>19.28</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1401,16 +1415,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>4461.35</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>20.78</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1420,16 +1434,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>4341.95</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>20.28</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1439,16 +1453,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>4297.15</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>20.08</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1458,16 +1472,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>4127.4</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>19.83</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1477,16 +1491,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>4097.7</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>16.24</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1496,16 +1510,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>4436.25</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>17.05</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1515,16 +1529,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>4625.15</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>18.76</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1534,16 +1548,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>4899.5</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>19.43</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1553,16 +1567,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>5294.75</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>22.84</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1572,16 +1586,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>5619.4</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>24.54</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1591,16 +1605,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>5883.3</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>25.39</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1610,16 +1624,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>5817.95</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>23.92</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1629,16 +1643,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>6539.5</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>26.43</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1648,16 +1662,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>7132.1</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>28.81</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1667,16 +1681,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>7435.4</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>29.3</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1686,16 +1700,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>7351.65</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>29.22</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1705,16 +1719,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>7029.95</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>22.83</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1724,16 +1738,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>7861.2</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>25.13</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1743,16 +1757,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>7726.75</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>23.65</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1762,16 +1776,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>8575.6</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>26.31</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1781,16 +1795,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>8946.9</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>27.2</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1800,16 +1814,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>9168.950000000001</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>27.62</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1819,16 +1833,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>9206.85</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>32.43</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1838,16 +1852,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>8986</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>32.16</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1857,16 +1871,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>8984.950000000001</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>31.12</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1876,16 +1890,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>8937.200000000001</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>30.88</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1895,16 +1909,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>8049.35</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>25.74</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1914,16 +1928,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>7095.75</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>22.14</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1933,16 +1947,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>7724.65</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>30.01</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1952,16 +1966,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>7943.4</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>30.9</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1971,16 +1985,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>8561.5</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>33.06</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1990,16 +2004,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>9187.299999999999</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>35.38</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2009,16 +2023,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>8671.85</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>33.4</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2028,16 +2042,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>8261.549999999999</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>32.41</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2047,16 +2061,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>8395.4</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>29.13</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2066,16 +2080,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>8842.65</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>30.56</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2085,16 +2099,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>8699.6</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>32.27</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2104,16 +2118,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>8606.1</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>31.9</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2123,16 +2137,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>8189.35</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>29.53</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2142,16 +2156,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>8302.299999999999</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>29.9</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2161,16 +2175,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>7465.05</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>24.26</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2180,16 +2194,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>8786.6</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>28.06</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2199,16 +2213,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>8951.35</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>30.16</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2218,16 +2232,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>9332.549999999999</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>31.84</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2237,16 +2251,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>9644.450000000001</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>31.87</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2256,16 +2270,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>9937.700000000001</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>31.81</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2367,13 +2381,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>3095.04</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>38.3</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2381,12 +2395,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,C2)+1)/2)/COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2394,31 +2408,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>3361.47</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>59.82</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2426,12 +2440,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,C3)+1)/2)/COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2439,28 +2453,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>3065.15</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>63.23</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2468,12 +2482,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,C4)+1)/2)/COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2481,28 +2495,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>3822.79</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>56.37</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2510,12 +2524,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,C5)+1)/2)/COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2523,28 +2537,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>4143.79</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>41.57</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2552,15 +2566,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,C6)+1)/2)/COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2568,28 +2582,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>4115.69</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>37.37</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2597,15 +2611,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,C7)+1)/2)/COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2613,28 +2627,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>4731.14</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>57.77</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2642,15 +2656,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,C8)+1)/2)/COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2658,28 +2672,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>3994.75</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>79.25</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2687,15 +2701,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,C9)+1)/2)/COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2703,42 +2717,42 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>3628.85</v>
       </c>
-      <c r="C10" s="7" t="n"/>
+      <c r="C10" s="25" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,C10)+1)/2)/COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2746,42 +2760,42 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>2963.3</v>
       </c>
-      <c r="C11" s="7" t="n"/>
+      <c r="C11" s="25" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,C11)+1)/2)/COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2789,28 +2803,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>3170.29</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>55.77</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2818,15 +2832,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,C12)+1)/2)/COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2834,28 +2848,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>3257.3</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>23.09</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2863,15 +2877,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,C13)+1)/2)/COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2879,28 +2893,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>2993.75</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>16.25</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2908,15 +2922,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,C14)+1)/2)/COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2924,28 +2938,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>2680.45</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>22.89</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2953,15 +2967,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,C15)+1)/2)/COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -2969,28 +2983,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>2813.2</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>22.73</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2998,15 +3012,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,C16)+1)/2)/COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3014,28 +3028,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>1743.15</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>13.57</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3043,15 +3057,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,C17)+1)/2)/COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3059,28 +3073,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>2178.2</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>17.83</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3088,15 +3102,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,C18)+1)/2)/COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3104,28 +3118,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>2911.4</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>29.31</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3133,15 +3147,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,C19)+1)/2)/COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3149,28 +3163,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>3535.05</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>36.74</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3178,15 +3192,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,C20)+1)/2)/COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3194,28 +3208,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>4055.4</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>64.36</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3223,15 +3237,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,C21)+1)/2)/COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3239,28 +3253,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>4891.35</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>60.54</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3268,15 +3282,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,C22)+1)/2)/COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3284,28 +3298,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>5340.7</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>29.25</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3313,15 +3327,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,C23)+1)/2)/COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3329,25 +3343,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>5330.75</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>33.52</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3355,15 +3369,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,C24)+1)/2)/COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3371,25 +3385,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>4801.45</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>31.59</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3397,15 +3411,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,C25)+1)/2)/COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3413,25 +3427,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>3848.55</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>22.84</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3439,15 +3453,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,C26)+1)/2)/COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3455,25 +3469,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>4265.9</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>19.04</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3481,15 +3495,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,C27)+1)/2)/COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3497,25 +3511,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>4341.95</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>20.28</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3523,15 +3537,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,C28)+1)/2)/COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3539,25 +3553,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>4097.7</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>16.24</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3565,15 +3579,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,C29)+1)/2)/COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3581,25 +3595,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>4899.5</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>19.43</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3607,15 +3621,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,C30)+1)/2)/COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3623,25 +3637,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>5883.3</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>25.39</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3649,15 +3663,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,C31)+1)/2)/COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3665,22 +3679,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>7132.1</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>28.81</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3688,15 +3702,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,C32)+1)/2)/COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3704,22 +3718,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>7029.95</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>22.83</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3727,15 +3741,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,C33)+1)/2)/COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3743,22 +3757,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>8575.6</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>26.31</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3766,15 +3780,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,C34)+1)/2)/COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3782,22 +3796,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>9206.85</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>32.43</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3805,15 +3819,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,C35)+1)/2)/COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3821,22 +3835,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>8937.200000000001</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>30.88</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3844,15 +3858,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,C36)+1)/2)/COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3860,22 +3874,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>7724.65</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>30.01</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3883,15 +3897,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,C37)+1)/2)/COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3899,22 +3913,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>9187.299999999999</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>35.38</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3922,15 +3936,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,C38)+1)/2)/COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3938,22 +3952,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>8395.4</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>29.13</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3961,15 +3975,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,C39)+1)/2)/COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -3977,19 +3991,19 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16" t="n"/>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="I39" s="30" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>8606.1</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>31.9</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3997,15 +4011,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,C40)+1)/2)/COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -4013,19 +4027,19 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="I40" s="30" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>7465.05</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>24.26</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4033,15 +4047,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,C41)+1)/2)/COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -4049,19 +4063,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>9332.549999999999</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>31.84</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4069,15 +4083,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,C42)+1)/2)/COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0"))</f>
         <v/>
       </c>
@@ -4085,10 +4099,10 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4165,30 +4179,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>9956.65</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>31.87</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.742424242424</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.225829820798</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4198,30 +4212,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>9948.15</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>31.85</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.734848484848</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.225578775388</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4231,30 +4245,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>9904.85</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>31.71</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.7045454545449999</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.225390109018</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4374,4 +4388,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Smallcap 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4287,6 +4290,1112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Smallcap 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aegis Logistics Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Affle 3i Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AFFLE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Amber Enterprises India Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anand Rathi Wealth Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Angel One Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bandhan Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Castrol India Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Central Depository Services (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CESC Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>City Union Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cohance Lifesciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>COHANCE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Computer Age Management Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Crompton Greaves Consumer Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Delhivery Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dr. Lal Path Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Five-Star Business Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FIVESTAR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gland Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hindustan Copper Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IIFL Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Indraprastha Gas Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Inox Wind Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Karur Vysya Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KARURVYSYA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kaynes Technology India Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kec International Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>KEC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kfin Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Manappuram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Narayana Hrudayalaya Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NATCO Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NATCOPHARM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Navin Fluorine International Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NBCC (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Neuland Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NEULANDLAB</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PG Electroplast Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Piramal Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PIRAMALFIN</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Piramal Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PNB Housing Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Poonawalla Fincorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RBL Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Redington Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reliance Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RPOWER</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sai Life Sciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sona BLW Precision Forgings Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Syngene International Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tata Chemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tata Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Welspun Corp Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Wockhardt Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WOCKPHARMA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4388,43 +5497,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Smallcap 50 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9904.85</v>
+        <v>10002.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.71</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.7045454545454546</v>
+        <v>0.7651515151515151</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>312.3573005361085</v>
+        <v>312.3828856964397</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2253901090176604</v>
+        <v>0.1809844912855247</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0315357931251971</v>
+        <v>0.03123048094940662</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>29.54545454545454</v>
+        <v>23.48484848484848</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>95.0780218035321</v>
+        <v>86.19689825710495</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.2052247228778</v>
+        <v>42.29846341652542</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.40412855101326</v>
+        <v>26.31143917030893</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8559.879617739</v>
+        <v>8219.243294847442</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1357890712389386</v>
+        <v>-0.1782811002401958</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.6427611943529</v>
+        <v>32.25560495373558</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10196.20476871291</v>
+        <v>10076.09895533229</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.02941536406032474</v>
+        <v>0.007358056019224568</v>
       </c>
     </row>
     <row r="16">
@@ -4120,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4277,6 +4277,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>10002.5</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.765151515152</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.180984491286</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>10002.5</v>
+        <v>9839.700000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>32.02</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.7651515151515151</v>
+        <v>0.6742424242424242</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>312.3828856964397</v>
+        <v>312.3714285714286</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1809844912855247</v>
+        <v>0.1810250762676202</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03123048094940662</v>
+        <v>0.03174603174603174</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>23.48484848484848</v>
+        <v>32.57575757575758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>86.19689825710495</v>
+        <v>86.20501525352404</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>42.29846341652542</v>
+        <v>48.66453487908751</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.31143917030893</v>
+        <v>26.31171050990352</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8219.243294847442</v>
+        <v>8219.026600136433</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1782811002401958</v>
+        <v>-0.1647076028602059</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.25560495373558</v>
+        <v>32.25585368169727</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10076.09895533229</v>
+        <v>10075.80709434275</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.007358056019224568</v>
+        <v>0.02399535497451666</v>
       </c>
     </row>
     <row r="16">
@@ -4120,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4310,6 +4310,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>9839.700000000001</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.674242424242</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.181025076268</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4350,7 +4383,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9839.700000000001</v>
+        <v>9883.450000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.5</v>
+        <v>31.64</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6742424242424242</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>312.3714285714286</v>
+        <v>312.371997471555</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1810250762676202</v>
+        <v>0.1808848879672436</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03174603174603174</v>
+        <v>0.0316055625790139</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>32.57575757575758</v>
+        <v>29.54545454545454</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>86.20501525352404</v>
+        <v>86.17697759344871</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>48.66453487908751</v>
+        <v>46.53491145985279</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.31171050990352</v>
+        <v>26.310773250981</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8219.026600136433</v>
+        <v>8218.748795430092</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1647076028602059</v>
+        <v>-0.1684332095138751</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.25585368169727</v>
+        <v>32.25499452768496</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10075.80709434275</v>
+        <v>10075.55706904703</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.02399535497451666</v>
+        <v>0.01943724803049829</v>
       </c>
     </row>
     <row r="16">
@@ -4120,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4343,6 +4343,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>9883.450000000001</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.7045454545449999</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.180884887967</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4383,7 +4416,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9883.450000000001</v>
+        <v>9696.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.64</v>
+        <v>31.04</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.7045454545454546</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>312.371997471555</v>
+        <v>312.3791881443299</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1808848879672436</v>
+        <v>0.181032426367274</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0316055625790139</v>
+        <v>0.03221649484536083</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>29.54545454545454</v>
+        <v>34.09090909090909</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>86.17697759344871</v>
+        <v>86.2064852734548</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>46.53491145985279</v>
+        <v>49.7255819456728</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.310773250981</v>
+        <v>26.31175965056977</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8218.748795430092</v>
+        <v>8219.246118293724</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1684332095138751</v>
+        <v>-0.1523273308450459</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.25499452768496</v>
+        <v>32.25589872730801</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10075.55706904703</v>
+        <v>10076.0714573022</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.01943724803049829</v>
+        <v>0.03917199508079916</v>
       </c>
     </row>
     <row r="16">
@@ -4120,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4376,6 +4376,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>9696.25</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.659090909091</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.181032426367</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4416,7 +4449,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9696.25</v>
+        <v>9628.049999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.04</v>
+        <v>30.82</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6590909090909091</v>
+        <v>0.6287878787878788</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>312.3791881443299</v>
+        <v>312.3961713173264</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.181032426367274</v>
+        <v>0.1812153466812101</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03221649484536083</v>
+        <v>0.03244646333549643</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>34.09090909090909</v>
+        <v>37.12121212121212</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>86.2064852734548</v>
+        <v>86.24306933624202</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.7255819456728</v>
+        <v>51.85776928572109</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.31175965056977</v>
+        <v>26.3129826035258</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8219.246118293724</v>
+        <v>8220.075021280876</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1523273308450459</v>
+        <v>-0.1462367747071446</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.25589872730801</v>
+        <v>32.2570197675177</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10076.0714573022</v>
+        <v>10076.96947347984</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.03917199508079916</v>
+        <v>0.04662620919914673</v>
       </c>
     </row>
     <row r="16">
@@ -4120,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4409,6 +4409,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>9628.049999999999</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.628787878788</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.181215346681</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4449,7 +4482,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4519,17 +4552,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd.</t>
+          <t>Acutaas Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4539,17 +4572,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>Aegis Logistics Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4559,17 +4592,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+          <t>Affle 3i Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -4579,17 +4612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4599,17 +4632,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4652,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Angel One Ltd.</t>
+          <t>Anand Rathi Wealth Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4639,17 +4672,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Ltd.</t>
+          <t>Angel One Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4659,17 +4692,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bandhan Bank Ltd.</t>
+          <t>Apollo Tyres Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4679,17 +4712,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Ather Energy Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Ltd.</t>
+          <t>Bandhan Bank Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4719,17 +4752,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>Central Depository Services (India) Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4772,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>City Union Bank Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4759,12 +4792,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>City Union Bank Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4779,17 +4812,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cohance Lifesciences Ltd.</t>
+          <t>Crompton Greaves Consumer Electricals Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -4799,17 +4832,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Delhivery Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4819,17 +4852,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crompton Greaves Consumer Electricals Ltd.</t>
+          <t>Dr. Lal Path Labs Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4839,17 +4872,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delhivery Ltd.</t>
+          <t>Gland Pharma Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4859,17 +4892,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>Great Eastern Shipping Co. Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4879,17 +4912,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>HFCL Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -4899,17 +4932,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gland Pharma Ltd.</t>
+          <t>Himadri Speciality Chemical Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>HSCL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -4919,17 +4952,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd.</t>
+          <t>IIFL Finance Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HSCL</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4939,17 +4972,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4992,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IIFL Finance Ltd.</t>
+          <t>Inox Wind Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4979,17 +5012,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4999,12 +5032,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inox Wind Ltd.</t>
+          <t>Kaynes Technology India Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5019,12 +5052,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Karur Vysya Bank Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5039,12 +5072,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kaynes Technology India Ltd.</t>
+          <t>Kirloskar Oil Eng Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5059,17 +5092,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kec International Ltd.</t>
+          <t>KPIT Technologies Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5079,12 +5112,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>Manappuram Finance Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5099,17 +5132,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Manappuram Finance Ltd.</t>
+          <t>MTAR Technologies Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5119,12 +5152,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5139,17 +5172,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5159,17 +5192,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>NBCC (India) Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -5179,17 +5212,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NBCC (India) Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5199,12 +5232,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>Onesource Specialty Pharma Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5239,17 +5272,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Piramal Finance Ltd.</t>
+          <t>Piramal Pharma Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5259,17 +5292,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Piramal Pharma Ltd.</t>
+          <t>PNB Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5312,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PNB Housing Finance Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5299,12 +5332,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>RBL Bank Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5319,17 +5352,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd.</t>
+          <t>Redington Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5339,17 +5372,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Redington Ltd.</t>
+          <t>Sai Life Sciences Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5359,17 +5392,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Reliance Power Ltd.</t>
+          <t>Sona BLW Precision Forgings Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RPOWER</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5412,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sai Life Sciences Ltd.</t>
+          <t>Syngene International Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5399,17 +5432,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sona BLW Precision Forgings Ltd.</t>
+          <t>Tata Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5419,17 +5452,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Syngene International Ltd.</t>
+          <t>Tata Elxsi Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5439,17 +5472,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Chemicals Ltd.</t>
+          <t>Tata Technologies Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5459,17 +5492,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Technologies Ltd.</t>
+          <t>TD Power Systems Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9628.049999999999</v>
+        <v>9632.950000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.82</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6287878787878788</v>
+        <v>0.9104477611940298</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>312.3961713173264</v>
+        <v>274.7561323445522</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1812153466812101</v>
+        <v>-0.04666291836043468</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03244646333549643</v>
+        <v>0.02852253280091272</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>37.12121212121212</v>
+        <v>8.955223880597018</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>86.24306933624202</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>51.85776928572109</v>
+        <v>12.26865671641791</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.3129826035258</v>
+        <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>8220.075021280876</v>
+        <v>5410.733263385217</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1462367747071446</v>
+        <v>-0.4383098361991687</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.2570197675177</v>
+        <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>10076.96947347984</v>
+        <v>8049.569660174396</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.04662620919914673</v>
+        <v>-0.164371281884117</v>
       </c>
     </row>
     <row r="16">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.1777069814551362</v>
+        <v>0.09882004850674608</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1615917918332266</v>
+        <v>0.167528937256227</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.2600859628423946</v>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.1622127236202262</v>
+        <v>0.200251632875541</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.1990509240348866</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.1453087958047855</v>
+        <v>0.1252064799508934</v>
       </c>
       <c r="F20" s="30" t="n">
         <v>0.1166920027361642</v>
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>-0.1126363834223368</v>
+        <v>-0.1003859238888405</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>-0.0105997250482171</v>
@@ -909,7 +909,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>-0.08813546435534414</v>
+        <v>-0.08439746291096839</v>
       </c>
       <c r="D22" s="30" t="n">
         <v>0.005035411055723138</v>
@@ -917,7 +917,9 @@
       <c r="E22" s="30" t="n">
         <v>0.1070272331117028</v>
       </c>
-      <c r="F22" s="30" t="n"/>
+      <c r="F22" s="30" t="n">
+        <v>0.1110228899906136</v>
+      </c>
       <c r="G22" s="30" t="n">
         <v>0.4285714285714285</v>
       </c>
@@ -936,7 +938,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -946,7 +948,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -969,7 +971,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2288,6 +2290,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>9632.950000000001</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2404,7 +2425,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,C2)+1)/2)/COUNTIFS($D$2:$D$42,D2,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$43,D2,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$43,D2,$C$2:$C$43,C2)+1)/2)/COUNTIFS($D$2:$D$43,D2,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2449,7 +2470,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,C3)+1)/2)/COUNTIFS($D$2:$D$42,D3,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$43,D3,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$43,D3,$C$2:$C$43,C3)+1)/2)/COUNTIFS($D$2:$D$43,D3,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2468,7 +2489,10 @@
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="30" t="n"/>
+      <c r="L3" s="30">
+        <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="n">
@@ -2491,7 +2515,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,C4)+1)/2)/COUNTIFS($D$2:$D$42,D4,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$43,D4,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$43,D4,$C$2:$C$43,C4)+1)/2)/COUNTIFS($D$2:$D$43,D4,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2533,7 +2557,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,C5)+1)/2)/COUNTIFS($D$2:$D$42,D5,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$43,D5,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$43,D5,$C$2:$C$43,C5)+1)/2)/COUNTIFS($D$2:$D$43,D5,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2578,7 +2602,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,C6)+1)/2)/COUNTIFS($D$2:$D$42,D6,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$43,D6,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$43,D6,$C$2:$C$43,C6)+1)/2)/COUNTIFS($D$2:$D$43,D6,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2623,7 +2647,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,C7)+1)/2)/COUNTIFS($D$2:$D$42,D7,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$43,D7,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$43,D7,$C$2:$C$43,C7)+1)/2)/COUNTIFS($D$2:$D$43,D7,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2668,7 +2692,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,C8)+1)/2)/COUNTIFS($D$2:$D$42,D8,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$43,D8,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$43,D8,$C$2:$C$43,C8)+1)/2)/COUNTIFS($D$2:$D$43,D8,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2713,7 +2737,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,C9)+1)/2)/COUNTIFS($D$2:$D$42,D9,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$43,D9,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$43,D9,$C$2:$C$43,C9)+1)/2)/COUNTIFS($D$2:$D$43,D9,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2756,7 +2780,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,C10)+1)/2)/COUNTIFS($D$2:$D$42,D10,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$43,D10,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$43,D10,$C$2:$C$43,C10)+1)/2)/COUNTIFS($D$2:$D$43,D10,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2799,7 +2823,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,C11)+1)/2)/COUNTIFS($D$2:$D$42,D11,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$43,D11,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$43,D11,$C$2:$C$43,C11)+1)/2)/COUNTIFS($D$2:$D$43,D11,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2844,7 +2868,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,C12)+1)/2)/COUNTIFS($D$2:$D$42,D12,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$43,D12,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$43,D12,$C$2:$C$43,C12)+1)/2)/COUNTIFS($D$2:$D$43,D12,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2889,7 +2913,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,C13)+1)/2)/COUNTIFS($D$2:$D$42,D13,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$43,D13,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$43,D13,$C$2:$C$43,C13)+1)/2)/COUNTIFS($D$2:$D$43,D13,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2934,7 +2958,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,C14)+1)/2)/COUNTIFS($D$2:$D$42,D14,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$43,D14,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$43,D14,$C$2:$C$43,C14)+1)/2)/COUNTIFS($D$2:$D$43,D14,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2979,7 +3003,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,C15)+1)/2)/COUNTIFS($D$2:$D$42,D15,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$43,D15,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$43,D15,$C$2:$C$43,C15)+1)/2)/COUNTIFS($D$2:$D$43,D15,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3024,7 +3048,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,C16)+1)/2)/COUNTIFS($D$2:$D$42,D16,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$43,D16,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$43,D16,$C$2:$C$43,C16)+1)/2)/COUNTIFS($D$2:$D$43,D16,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3069,7 +3093,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,C17)+1)/2)/COUNTIFS($D$2:$D$42,D17,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$43,D17,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$43,D17,$C$2:$C$43,C17)+1)/2)/COUNTIFS($D$2:$D$43,D17,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3114,7 +3138,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,C18)+1)/2)/COUNTIFS($D$2:$D$42,D18,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$43,D18,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$43,D18,$C$2:$C$43,C18)+1)/2)/COUNTIFS($D$2:$D$43,D18,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3159,7 +3183,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,C19)+1)/2)/COUNTIFS($D$2:$D$42,D19,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$43,D19,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$43,D19,$C$2:$C$43,C19)+1)/2)/COUNTIFS($D$2:$D$43,D19,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3204,7 +3228,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,C20)+1)/2)/COUNTIFS($D$2:$D$42,D20,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$43,D20,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$43,D20,$C$2:$C$43,C20)+1)/2)/COUNTIFS($D$2:$D$43,D20,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3249,7 +3273,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,C21)+1)/2)/COUNTIFS($D$2:$D$42,D21,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$43,D21,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$43,D21,$C$2:$C$43,C21)+1)/2)/COUNTIFS($D$2:$D$43,D21,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3294,7 +3318,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,C22)+1)/2)/COUNTIFS($D$2:$D$42,D22,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$43,D22,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$43,D22,$C$2:$C$43,C22)+1)/2)/COUNTIFS($D$2:$D$43,D22,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3339,7 +3363,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,C23)+1)/2)/COUNTIFS($D$2:$D$42,D23,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$43,D23,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$43,D23,$C$2:$C$43,C23)+1)/2)/COUNTIFS($D$2:$D$43,D23,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3354,7 +3378,10 @@
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="30" t="n"/>
+      <c r="K23" s="30">
+        <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
@@ -3381,7 +3408,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,C24)+1)/2)/COUNTIFS($D$2:$D$42,D24,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$43,D24,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$43,D24,$C$2:$C$43,C24)+1)/2)/COUNTIFS($D$2:$D$43,D24,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3423,7 +3450,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,C25)+1)/2)/COUNTIFS($D$2:$D$42,D25,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$43,D25,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$43,D25,$C$2:$C$43,C25)+1)/2)/COUNTIFS($D$2:$D$43,D25,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3465,7 +3492,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,C26)+1)/2)/COUNTIFS($D$2:$D$42,D26,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$43,D26,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$43,D26,$C$2:$C$43,C26)+1)/2)/COUNTIFS($D$2:$D$43,D26,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3507,7 +3534,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,C27)+1)/2)/COUNTIFS($D$2:$D$42,D27,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$43,D27,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$43,D27,$C$2:$C$43,C27)+1)/2)/COUNTIFS($D$2:$D$43,D27,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3549,7 +3576,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,C28)+1)/2)/COUNTIFS($D$2:$D$42,D28,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$43,D28,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$43,D28,$C$2:$C$43,C28)+1)/2)/COUNTIFS($D$2:$D$43,D28,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3591,7 +3618,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,C29)+1)/2)/COUNTIFS($D$2:$D$42,D29,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$43,D29,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$43,D29,$C$2:$C$43,C29)+1)/2)/COUNTIFS($D$2:$D$43,D29,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3633,7 +3660,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,C30)+1)/2)/COUNTIFS($D$2:$D$42,D30,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$43,D30,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$43,D30,$C$2:$C$43,C30)+1)/2)/COUNTIFS($D$2:$D$43,D30,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3675,7 +3702,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,C31)+1)/2)/COUNTIFS($D$2:$D$42,D31,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$43,D31,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$43,D31,$C$2:$C$43,C31)+1)/2)/COUNTIFS($D$2:$D$43,D31,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3686,7 +3713,10 @@
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="30" t="n"/>
+      <c r="J31" s="30">
+        <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K31" s="30" t="n"/>
       <c r="L31" s="30" t="n"/>
     </row>
@@ -3714,7 +3744,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,C32)+1)/2)/COUNTIFS($D$2:$D$42,D32,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$43,D32,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$43,D32,$C$2:$C$43,C32)+1)/2)/COUNTIFS($D$2:$D$43,D32,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3753,7 +3783,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,C33)+1)/2)/COUNTIFS($D$2:$D$42,D33,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$43,D33,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$43,D33,$C$2:$C$43,C33)+1)/2)/COUNTIFS($D$2:$D$43,D33,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3792,7 +3822,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,C34)+1)/2)/COUNTIFS($D$2:$D$42,D34,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$43,D34,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$43,D34,$C$2:$C$43,C34)+1)/2)/COUNTIFS($D$2:$D$43,D34,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3831,7 +3861,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,C35)+1)/2)/COUNTIFS($D$2:$D$42,D35,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$43,D35,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$43,D35,$C$2:$C$43,C35)+1)/2)/COUNTIFS($D$2:$D$43,D35,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3870,7 +3900,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,C36)+1)/2)/COUNTIFS($D$2:$D$42,D36,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$43,D36,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$43,D36,$C$2:$C$43,C36)+1)/2)/COUNTIFS($D$2:$D$43,D36,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3909,7 +3939,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,C37)+1)/2)/COUNTIFS($D$2:$D$42,D37,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$43,D37,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$43,D37,$C$2:$C$43,C37)+1)/2)/COUNTIFS($D$2:$D$43,D37,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3948,7 +3978,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,C38)+1)/2)/COUNTIFS($D$2:$D$42,D38,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$43,D38,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$43,D38,$C$2:$C$43,C38)+1)/2)/COUNTIFS($D$2:$D$43,D38,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -3987,14 +4017,17 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,C39)+1)/2)/COUNTIFS($D$2:$D$42,D39,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$43,D39,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$43,D39,$C$2:$C$43,C39)+1)/2)/COUNTIFS($D$2:$D$43,D39,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="30" t="n"/>
+      <c r="I39" s="30">
+        <f>IFERROR(B43/B39-1,"")</f>
+        <v/>
+      </c>
       <c r="J39" s="30" t="n"/>
       <c r="K39" s="30" t="n"/>
       <c r="L39" s="30" t="n"/>
@@ -4023,7 +4056,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,C40)+1)/2)/COUNTIFS($D$2:$D$42,D40,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$43,D40,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$43,D40,$C$2:$C$43,C40)+1)/2)/COUNTIFS($D$2:$D$43,D40,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4059,7 +4092,7 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,C41)+1)/2)/COUNTIFS($D$2:$D$42,D41,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$43,D41,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$43,D41,$C$2:$C$43,C41)+1)/2)/COUNTIFS($D$2:$D$43,D41,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
@@ -4095,7 +4128,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0",$C$2:$C$42,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,C42)+1)/2)/COUNTIFS($D$2:$D$42,D42,$C$2:$C$42,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$43,D42,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$43,D42,$C$2:$C$43,C42)+1)/2)/COUNTIFS($D$2:$D$43,D42,$C$2:$C$43,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4106,6 +4139,42 @@
       <c r="J42" s="30" t="n"/>
       <c r="K42" s="30" t="n"/>
       <c r="L42" s="30" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B43" s="24" t="n">
+        <v>9632.950000000001</v>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E43" s="33">
+        <f>IFERROR(B43/C43,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="30">
+        <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="30">
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$43,D43,$C$2:$C$43,"&gt;0",$C$2:$C$43,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$43,D43,$C$2:$C$43,C43)+1)/2)/COUNTIFS($D$2:$D$43,D43,$C$2:$C$43,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4120,15 +4189,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4442,6 +4511,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>9632.950000000001</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.9104477611939999</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>-0.0466629183604</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4482,7 +4584,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9632.950000000001</v>
+        <v>9534.700000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.06</v>
+        <v>34.73</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9104477611940298</v>
+        <v>0.9029850746268657</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.7561323445522</v>
+        <v>274.5378635185719</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04666291836043468</v>
+        <v>-0.04743180126929536</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02852253280091272</v>
+        <v>0.02879355024474518</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>8.955223880597018</v>
+        <v>9.701492537313428</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>12.26865671641791</v>
+        <v>12.7910447761194</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5410.733263385217</v>
+        <v>5406.434926576448</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4383098361991687</v>
+        <v>-0.4329727283945539</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8049.569660174396</v>
+        <v>8043.17500719839</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.164371281884117</v>
+        <v>-0.1564312451153798</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4544,6 +4544,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>9534.700000000001</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>34.73</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.902985074627</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>-0.0474318012693</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4584,7 +4617,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9534.700000000001</v>
+        <v>9560.950000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.73</v>
+        <v>34.83</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.5378635185719</v>
+        <v>274.5033017513638</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04743180126929536</v>
+        <v>-0.04770277101717557</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02879355024474518</v>
+        <v>0.02871088142405972</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5406.434926576448</v>
+        <v>5405.754306632214</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4329727283945539</v>
+        <v>-0.4346007136704811</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8043.17500719839</v>
+        <v>8042.162446167098</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1564312451153798</v>
+        <v>-0.1588532053648333</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4577,6 +4577,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>9560.950000000001</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.902985074627</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>-0.0477027710172</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4617,7 +4650,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9560.950000000001</v>
+        <v>9700.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.83</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9029850746268657</v>
+        <v>0.917910447761194</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.5033017513638</v>
+        <v>274.5019807583474</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04770277101717557</v>
+        <v>-0.04748970831839283</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02871088142405972</v>
+        <v>0.02829654782116581</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>9.701492537313428</v>
+        <v>8.208955223880599</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>12.7910447761194</v>
+        <v>11.74626865671642</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5405.754306632214</v>
+        <v>5405.728292505456</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4346007136704811</v>
+        <v>-0.4427601261217561</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8042.162446167098</v>
+        <v>8042.123744845985</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1588532053648333</v>
+        <v>-0.1709919961193307</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4610,6 +4610,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>9700.9</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.9179104477609999</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>-0.0474897083184</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4650,7 +4683,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9700.9</v>
+        <v>9728.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.34</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.917910447761194</v>
+        <v>0.9328358208955224</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.5019807583474</v>
+        <v>274.5062076749436</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04748970831839283</v>
+        <v>-0.04765208951420641</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02829654782116581</v>
+        <v>0.02821670428893906</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>8.208955223880599</v>
+        <v>6.716417910447758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>11.74626865671642</v>
+        <v>10.70149253731343</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5405.728292505456</v>
+        <v>5405.811532570139</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4427601261217561</v>
+        <v>-0.4443324733956787</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8042.123744845985</v>
+        <v>8042.247581425348</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1709919961193307</v>
+        <v>-0.173331183489197</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4643,6 +4643,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>9728.5</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.932835820896</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.0476520895142</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4683,7 +4716,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9728.5</v>
+        <v>9486.799999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.44</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9328358208955224</v>
+        <v>0.8880597014925373</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.5062076749436</v>
+        <v>274.5023148148148</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04765208951420641</v>
+        <v>-0.04772540452495377</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02821670428893906</v>
+        <v>0.02893518518518518</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>6.716417910447758</v>
+        <v>11.19402985074627</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>10.70149253731343</v>
+        <v>13.83582089552239</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5405.811532570139</v>
+        <v>5405.734871031746</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4443324733956787</v>
+        <v>-0.4301835317460317</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8042.247581425348</v>
+        <v>8042.133531746032</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.173331183489197</v>
+        <v>-0.1522817460317459</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4676,6 +4676,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>9486.799999999999</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.888059701493</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>-0.047725404525</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4716,7 +4749,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9486.799999999999</v>
+        <v>9550.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.56</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.8880597014925373</v>
+        <v>0.9029850746268657</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.5023148148148</v>
+        <v>274.515665421098</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04772540452495377</v>
+        <v>-0.04761824583684626</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02893518518518518</v>
+        <v>0.02874389192296637</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>11.19402985074627</v>
+        <v>9.701492537313428</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>13.83582089552239</v>
+        <v>12.7910447761194</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5405.734871031746</v>
+        <v>5405.997782614051</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4301835317460317</v>
+        <v>-0.433950642631298</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8042.133531746032</v>
+        <v>8042.52466636554</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1522817460317459</v>
+        <v>-0.1578860920625795</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4709,6 +4709,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>9550.4</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.902985074627</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.0476182458368</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4749,7 +4782,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9550.4</v>
+        <v>9698.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.79</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9029850746268657</v>
+        <v>0.917910447761194</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.515665421098</v>
+        <v>274.5075007076139</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04761824583684626</v>
+        <v>-0.04744482959704288</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02874389192296637</v>
+        <v>0.02830455703368243</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>9.701492537313428</v>
+        <v>8.208955223880599</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>12.7910447761194</v>
+        <v>11.74626865671642</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5405.997782614051</v>
+        <v>5405.836996077797</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.433950642631298</v>
+        <v>-0.4426024018438397</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8042.52466636554</v>
+        <v>8042.285463588209</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1578860920625795</v>
+        <v>-0.1707573490760583</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4742,6 +4742,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>9698.35</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.9179104477609999</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.047444829597</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4782,7 +4815,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9698.35</v>
+        <v>9732.299999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.33</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>274.5075007076139</v>
+        <v>277.1945314725149</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.04744482959704288</v>
+        <v>-0.0381800531277372</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02830455703368243</v>
+        <v>0.02848191398461977</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5405.836996077797</v>
+        <v>5458.752309069455</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4426024018438397</v>
+        <v>-0.4391097367457378</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8042.285463588209</v>
+        <v>8121.007787769053</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1707573490760583</v>
+        <v>-0.1655612971477396</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4775,6 +4775,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>9732.299999999999</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.9179104477609999</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.0381800531277</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4815,7 +4848,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9732.299999999999</v>
+        <v>9678.950000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.11</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.917910447761194</v>
+        <v>0.9029850746268657</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>277.1945314725149</v>
+        <v>277.3338108882522</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.0381800531277372</v>
+        <v>-0.03759121225885587</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02848191398461977</v>
+        <v>0.02865329512893983</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>8.208955223880599</v>
+        <v>9.701492537313428</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>11.74626865671642</v>
+        <v>12.7910447761194</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5458.752309069455</v>
+        <v>5461.495118706509</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4391097367457378</v>
+        <v>-0.4357347523536635</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8121.007787769053</v>
+        <v>8125.088276708965</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1655612971477396</v>
+        <v>-0.1605403192795742</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4808,6 +4808,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>9678.950000000001</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.902985074627</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>-0.0375912122589</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4848,7 +4881,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9678.950000000001</v>
+        <v>9571.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.9</v>
+        <v>34.51</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.9029850746268657</v>
+        <v>0.8880597014925373</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>277.3338108882522</v>
+        <v>277.361634308896</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.03759121225885587</v>
+        <v>-0.0375156951561183</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02865329512893983</v>
+        <v>0.02897710808461316</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>9.701492537313428</v>
+        <v>11.19402985074627</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>12.7910447761194</v>
+        <v>13.83582089552239</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5461.495118706509</v>
+        <v>5462.043041354473</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4357347523536635</v>
+        <v>-0.4293579500765824</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8125.088276708965</v>
+        <v>8125.903423438342</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1605403192795742</v>
+        <v>-0.1510535248582191</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4841,6 +4841,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>9571.75</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.888059701493</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>-0.0375156951561</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4881,7 +4914,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9571.75</v>
+        <v>9583.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.51</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>277.361634308896</v>
+        <v>283.109305760709</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.0375156951561183</v>
+        <v>-0.01761768883828763</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02897710808461316</v>
+        <v>0.02954209748892171</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5462.043041354473</v>
+        <v>5575.231114159105</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4293579500765824</v>
+        <v>-0.4182316944503059</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8125.903423438342</v>
+        <v>8294.293775058029</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1510535248582191</v>
+        <v>-0.1345009495674192</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4874,6 +4874,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>9583.25</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.888059701493</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>-0.0176176888383</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4914,7 +4947,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9583.25</v>
+        <v>9525.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>33.85</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>283.109305760709</v>
+        <v>283.3387864366449</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.01761768883828763</v>
+        <v>-0.01560605447562713</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02954209748892171</v>
+        <v>0.0297441998810232</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5575.231114159105</v>
+        <v>5579.750244327357</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4182316944503059</v>
+        <v>-0.4142517209144216</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8294.293775058029</v>
+        <v>8301.016903203878</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1345009495674192</v>
+        <v>-0.1285799269142515</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4907,6 +4907,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>9525.85</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.888059701493</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>-0.0156060544756</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4947,7 +4980,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9525.85</v>
+        <v>9304.700000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>33.62</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.8880597014925373</v>
+        <v>0.8134328358208955</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>283.3387864366449</v>
+        <v>283.3343483556638</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.01560605447562713</v>
+        <v>-0.02210814184416965</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0297441998810232</v>
+        <v>0.03045066991473812</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>11.19402985074627</v>
+        <v>18.65671641791045</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>13.83582089552239</v>
+        <v>19.05970149253731</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5579.750244327357</v>
+        <v>5579.662845832608</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4142517209144216</v>
+        <v>-0.4003393074647643</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8301.016903203878</v>
+        <v>8300.886880111362</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1285799269142515</v>
+        <v>-0.1078823734122152</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4940,6 +4940,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>9304.700000000001</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.813432835821</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>-0.0221081418442</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4980,7 +5013,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9304.700000000001</v>
+        <v>9214.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>32.84</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.8134328358208955</v>
+        <v>0.7686567164179104</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>283.3343483556638</v>
+        <v>286.3455562461156</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.02210814184416965</v>
+        <v>-0.01171534726639711</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03045066991473812</v>
+        <v>0.03107520198881293</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>18.65671641791045</v>
+        <v>23.13432835820895</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>19.05970149253731</v>
+        <v>22.19402985074627</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5579.662845832608</v>
+        <v>5638.96213264672</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4003393074647643</v>
+        <v>-0.3880404865488769</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8300.886880111362</v>
+        <v>8389.106667850485</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1078823734122152</v>
+        <v>-0.08958536801917771</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4973,6 +4973,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>9214.6</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.768656716418</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>-0.0117153472664</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5013,7 +5046,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9214.6</v>
+        <v>8924.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>32.18</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.7686567164179104</v>
+        <v>0.664179104477612</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>286.3455562461156</v>
+        <v>286.3249919794674</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.01171534726639711</v>
+        <v>-0.0117485489130893</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03107520198881293</v>
+        <v>0.03208213025344882</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>23.13432835820895</v>
+        <v>33.58208955223881</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>22.19402985074627</v>
+        <v>29.50746268656716</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5638.96213264672</v>
+        <v>5638.55716348137</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3880404865488769</v>
+        <v>-0.368211192080297</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8389.106667850485</v>
+        <v>8388.50419359274</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.08958536801917771</v>
+        <v>-0.0600852468032449</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5006,6 +5006,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>8924.75</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.664179104478</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>-0.0117485489131</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5046,7 +5079,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>8924.75</v>
+        <v>9067.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.17</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.664179104477612</v>
+        <v>0.6940298507462687</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>286.3249919794674</v>
+        <v>286.3897662665825</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.0117485489130893</v>
+        <v>-0.01167376537576847</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03208213025344882</v>
+        <v>0.03158559696778269</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>33.58208955223881</v>
+        <v>30.59701492537313</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>29.50746268656716</v>
+        <v>27.41791044776119</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5638.55716348137</v>
+        <v>5639.832754264056</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.368211192080297</v>
+        <v>-0.3779893511415937</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8388.50419359274</v>
+        <v>8390.401895135819</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.0600852468032449</v>
+        <v>-0.07463225340673219</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5039,6 +5039,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>9067.1</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.694029850746</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>-0.0116737653758</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5079,7 +5112,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9067.1</v>
+        <v>9307.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>31.66</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6940298507462687</v>
+        <v>0.8134328358208955</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>286.3897662665825</v>
+        <v>286.3969230769231</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.01167376537576847</v>
+        <v>-0.01204587669900059</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03158559696778269</v>
+        <v>0.03076923076923077</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>30.59701492537313</v>
+        <v>18.65671641791045</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>27.41791044776119</v>
+        <v>19.05970149253731</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5639.832754264056</v>
+        <v>5639.973692307693</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3779893511415937</v>
+        <v>-0.394065934065934</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8390.401895135819</v>
+        <v>8390.61156923077</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.07463225340673219</v>
+        <v>-0.09854945054945041</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5072,6 +5072,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>9307.9</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.813432835821</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>-0.012045876699</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5112,7 +5145,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9307.9</v>
+        <v>9428.200000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>32.5</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>286.3969230769231</v>
+        <v>288.7656967840736</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.01204587669900059</v>
+        <v>-0.003986402236234698</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03076923076923077</v>
+        <v>0.03062787136294028</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5639.973692307693</v>
+        <v>5686.621614526362</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.394065934065934</v>
+        <v>-0.3968497046598118</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8390.61156923077</v>
+        <v>8460.009870925402</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.09854945054945041</v>
+        <v>-0.1026908772697439</v>
       </c>
     </row>
     <row r="16">
@@ -4189,14 +4189,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
@@ -5105,6 +5105,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>9428.200000000001</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.813432835821</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>-0.00398640223623</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5145,7 +5178,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9428.200000000001</v>
+        <v>9519.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>32.65</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>288.7656967840736</v>
+        <v>288.6340206185567</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003986402236234698</v>
+        <v>-0.003009229850447492</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03062787136294028</v>
+        <v>0.03032140691328078</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5686.621614526362</v>
+        <v>5684.02853460972</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3968497046598118</v>
+        <v>-0.4028848652863207</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8460.009870925402</v>
+        <v>8456.152135493372</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1026908772697439</v>
+        <v>-0.1116694100320541</v>
       </c>
     </row>
     <row r="16">
@@ -4189,7 +4189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5138,6 +5138,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>9519.15</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.813432835821</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>-0.00300922985045</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5178,7 +5211,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-smallcap-50.xlsx
+++ b/docs/downloads/indices/nifty-smallcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>9519.15</v>
+        <v>9363.549999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>32.98</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.8134328358208955</v>
+        <v>0.7686567164179104</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>288.6340206185567</v>
+        <v>290.3426356589147</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>-0.003009229850447492</v>
+        <v>-0.0007346777193943943</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03032140691328078</v>
+        <v>0.0310077519379845</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>18.65671641791045</v>
+        <v>23.13432835820895</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>19.05970149253731</v>
+        <v>22.19402985074627</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>19.69285714285714</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>5684.02853460972</v>
+        <v>5717.676046511628</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.4028848652863207</v>
+        <v>-0.3893687707641196</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>29.29714285714286</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>8456.152135493372</v>
+        <v>8506.209674418606</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>-0.1116694100320541</v>
+        <v>-0.09156146179401981</v>
       </c>
     </row>
     <row r="16">
@@ -4189,14 +4189,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
@@ -5171,6 +5171,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>9363.549999999999</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.768656716418</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>-0.000734677719394</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5211,7 +5244,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
